--- a/AAII_Financials/Yearly/PRTA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PRTA_YR_FIN.xlsx
@@ -2369,10 +2369,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7000</v>
+        <v>1800</v>
       </c>
       <c r="E45" s="3">
-        <v>13200</v>
+        <v>1200</v>
       </c>
       <c r="F45" s="3">
         <v>13100</v>
